--- a/Results.xlsx
+++ b/Results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/44fff8a7ed051f2c/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HK3\CS112\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="8_{73426F35-4547-478F-8B21-52702C38170D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FABA313-BCF7-4C53-A7A8-9F7F3958EBBF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC41E588-7340-4132-AC66-AE38B38F87BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{968BA774-B6AD-450E-B889-28B196FD10BB}"/>
   </bookViews>
@@ -138,9 +138,6 @@
     <t>Bài làm an toàn, mọi thứ đều ở mức khá. Thiếu điểm nhấn.</t>
   </si>
   <si>
-    <t>Code tốt, sạch. Nhưng phần báo cáo lý thuyết viết ngắn quá.</t>
-  </si>
-  <si>
     <t>Ý tưởng "Rank" hơi phức tạp hóa. Đánh giá độ phức tạp chưa thuyết phục.</t>
   </si>
   <si>
@@ -163,6 +160,9 @@
   </si>
   <si>
     <t>Làm tròn vai, kết quả đúng.  Báo cáo trình bày còn cơ bản.</t>
+  </si>
+  <si>
+    <t>Code tốt, sạch. Chứng minh chặt chẽ.</t>
   </si>
 </sst>
 </file>
@@ -824,7 +824,7 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -851,7 +851,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -878,7 +878,7 @@
         <v>8.5</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -989,7 +989,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>9</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1043,7 +1043,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -1051,23 +1051,23 @@
         <v>15</v>
       </c>
       <c r="C15" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D15" s="1">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
       <c r="F15" s="1">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G15" s="3">
         <f t="shared" si="0"/>
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -1094,7 +1094,7 @@
         <v>9.1</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -1121,7 +1121,7 @@
         <v>9.6</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -1148,7 +1148,7 @@
         <v>10</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -1175,7 +1175,7 @@
         <v>9.1</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
